--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,414 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123406741</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483402</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6842945</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123406779</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483392</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6842965</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123406891</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78848</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>864</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483324</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6843025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123406894</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57634</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6843017</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406741</v>
+        <v>123406894</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483402</v>
+        <v>483287</v>
       </c>
       <c r="R3" t="n">
-        <v>6842945</v>
+        <v>6843017</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,19 +876,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406779</v>
+        <v>123406741</v>
       </c>
       <c r="B4" t="n">
         <v>98368</v>
@@ -924,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483392</v>
+        <v>483402</v>
       </c>
       <c r="R4" t="n">
-        <v>6842965</v>
+        <v>6842945</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +978,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406894</v>
+        <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483287</v>
+        <v>483392</v>
       </c>
       <c r="R6" t="n">
-        <v>6843017</v>
+        <v>6842965</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406894</v>
+        <v>123406891</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>78850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483287</v>
+        <v>483324</v>
       </c>
       <c r="R3" t="n">
-        <v>6843017</v>
+        <v>6843025</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406741</v>
+        <v>123406894</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483402</v>
+        <v>483287</v>
       </c>
       <c r="R4" t="n">
-        <v>6842945</v>
+        <v>6843017</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>78848</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R5" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,7 +1095,7 @@
         <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>123406891</v>
       </c>
       <c r="B3" t="n">
-        <v>78850</v>
+        <v>78851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406891</v>
+        <v>123406779</v>
       </c>
       <c r="B3" t="n">
-        <v>78851</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483324</v>
+        <v>483392</v>
       </c>
       <c r="R3" t="n">
-        <v>6843025</v>
+        <v>6842965</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406894</v>
+        <v>123406891</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>78854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483287</v>
+        <v>483324</v>
       </c>
       <c r="R4" t="n">
-        <v>6843017</v>
+        <v>6843025</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406741</v>
+        <v>123406894</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +1002,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483402</v>
+        <v>483287</v>
       </c>
       <c r="R5" t="n">
-        <v>6842945</v>
+        <v>6843017</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406779</v>
+        <v>123406741</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,17 +1128,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483392</v>
+        <v>483402</v>
       </c>
       <c r="R6" t="n">
-        <v>6842965</v>
+        <v>6842945</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>123406779</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B4" t="n">
-        <v>78854</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R4" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -993,7 +993,7 @@
         <v>123406894</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406741</v>
+        <v>123406891</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>78860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483402</v>
+        <v>483324</v>
       </c>
       <c r="R6" t="n">
-        <v>6842945</v>
+        <v>6843025</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406779</v>
+        <v>123406894</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483392</v>
+        <v>483287</v>
       </c>
       <c r="R3" t="n">
-        <v>6842965</v>
+        <v>6843017</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406741</v>
+        <v>123406891</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>78865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483402</v>
+        <v>483324</v>
       </c>
       <c r="R4" t="n">
-        <v>6842945</v>
+        <v>6843025</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406894</v>
+        <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +1002,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483287</v>
+        <v>483402</v>
       </c>
       <c r="R5" t="n">
-        <v>6843017</v>
+        <v>6842945</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406891</v>
+        <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>78860</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483324</v>
+        <v>483392</v>
       </c>
       <c r="R6" t="n">
-        <v>6843025</v>
+        <v>6842965</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>123406894</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406891</v>
+        <v>123406779</v>
       </c>
       <c r="B4" t="n">
-        <v>78865</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483324</v>
+        <v>483392</v>
       </c>
       <c r="R4" t="n">
-        <v>6843025</v>
+        <v>6842965</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,12 +978,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -993,7 +993,7 @@
         <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406779</v>
+        <v>123406891</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>78867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483392</v>
+        <v>483324</v>
       </c>
       <c r="R6" t="n">
-        <v>6842965</v>
+        <v>6843025</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406779</v>
+        <v>123406741</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483392</v>
+        <v>483402</v>
       </c>
       <c r="R4" t="n">
-        <v>6842965</v>
+        <v>6842945</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406741</v>
+        <v>123406891</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>78867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483402</v>
+        <v>483324</v>
       </c>
       <c r="R5" t="n">
-        <v>6842945</v>
+        <v>6843025</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406891</v>
+        <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483324</v>
+        <v>483392</v>
       </c>
       <c r="R6" t="n">
-        <v>6843025</v>
+        <v>6842965</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406741</v>
+        <v>123406891</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>78867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483402</v>
+        <v>483324</v>
       </c>
       <c r="R4" t="n">
-        <v>6842945</v>
+        <v>6843025</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R5" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406894</v>
+        <v>123406779</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483287</v>
+        <v>483392</v>
       </c>
       <c r="R3" t="n">
-        <v>6843017</v>
+        <v>6842965</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B4" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R4" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406741</v>
+        <v>123406894</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +1002,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483402</v>
+        <v>483287</v>
       </c>
       <c r="R5" t="n">
-        <v>6842945</v>
+        <v>6843017</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406779</v>
+        <v>123406891</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>78867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483392</v>
+        <v>483324</v>
       </c>
       <c r="R6" t="n">
-        <v>6842965</v>
+        <v>6843025</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406779</v>
+        <v>123406894</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483392</v>
+        <v>483287</v>
       </c>
       <c r="R3" t="n">
-        <v>6842965</v>
+        <v>6843017</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406741</v>
+        <v>123406891</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>78867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483402</v>
+        <v>483324</v>
       </c>
       <c r="R4" t="n">
-        <v>6842945</v>
+        <v>6843025</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406894</v>
+        <v>123406779</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483287</v>
+        <v>483392</v>
       </c>
       <c r="R5" t="n">
-        <v>6843017</v>
+        <v>6842965</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B6" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R6" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406894</v>
+        <v>123406741</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483287</v>
+        <v>483402</v>
       </c>
       <c r="R3" t="n">
-        <v>6843017</v>
+        <v>6842945</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +876,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406779</v>
+        <v>123406894</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483392</v>
+        <v>483287</v>
       </c>
       <c r="R5" t="n">
-        <v>6842965</v>
+        <v>6843017</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406741</v>
+        <v>123406779</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1128,17 +1128,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483402</v>
+        <v>483392</v>
       </c>
       <c r="R6" t="n">
-        <v>6842945</v>
+        <v>6842965</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123406741</v>
+        <v>123406779</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -822,17 +822,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483402</v>
+        <v>483392</v>
       </c>
       <c r="R3" t="n">
-        <v>6842945</v>
+        <v>6842965</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B4" t="n">
-        <v>78867</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R4" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406894</v>
+        <v>123406891</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>78867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,37 +1006,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483287</v>
+        <v>483324</v>
       </c>
       <c r="R5" t="n">
-        <v>6843017</v>
+        <v>6843025</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1080,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406779</v>
+        <v>123406894</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483392</v>
+        <v>483287</v>
       </c>
       <c r="R6" t="n">
-        <v>6842965</v>
+        <v>6843017</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182849</v>
+        <v>123406891</v>
       </c>
       <c r="B2" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483309</v>
+        <v>483324</v>
       </c>
       <c r="R2" t="n">
-        <v>6842967</v>
+        <v>6843025</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,12 +775,7 @@
         <v>123406894</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123406779</v>
+        <v>112182849</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,20 +897,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hangaslamm, Hangaslamm, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483392</v>
+        <v>483309</v>
       </c>
       <c r="R4" t="n">
-        <v>6842965</v>
+        <v>6842967</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +938,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,49 +963,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406891</v>
+        <v>123406741</v>
       </c>
       <c r="B5" t="n">
-        <v>78889</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483324</v>
+        <v>483402</v>
       </c>
       <c r="R5" t="n">
-        <v>6843025</v>
+        <v>6842945</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,15 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123406741</v>
+        <v>123406779</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,17 +1103,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsberget, Blåbärsberget, Dlr</t>
+          <t>Hangaslamm, Hangaslamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483402</v>
+        <v>483392</v>
       </c>
       <c r="R6" t="n">
-        <v>6842945</v>
+        <v>6842965</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30610-2023 artfynd.xlsx
+++ b/artfynd/A 30610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406891</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182849</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>